--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260829_023248.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260829_023248.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260829_023248.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260829_023248.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
